--- a/artfynd/A 15155-2025 artfynd.xlsx
+++ b/artfynd/A 15155-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111466752</v>
+        <v>113539153</v>
       </c>
       <c r="B2" t="n">
-        <v>85134</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>249254</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mospindling</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius areni-silvae</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brandrud) Brandrud</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nietsavaara nordväst-E10, Lu lm</t>
+          <t>Nietsavaara, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>756581.7378500081</v>
+        <v>756859</v>
       </c>
       <c r="R2" t="n">
-        <v>7458606.401171698</v>
+        <v>7458449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,21 +770,16 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111466702</v>
+        <v>112022147</v>
       </c>
       <c r="B3" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nietsavaara nordväst-E10, Lu lm</t>
+          <t>Nietsavaara, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>756583.9747418021</v>
+        <v>756852</v>
       </c>
       <c r="R3" t="n">
-        <v>7458603.485325959</v>
+        <v>7458471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,17 +861,1131 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112022148</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90932</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nietsavaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>756758</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7458432</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112376561</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>väster om Nietsavaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>756747</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7458442</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112376510</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>väster om Nietsavaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>756797</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7458467</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111466666</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87325</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vaxspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius pinophilus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nietsavaara nordväst-E10, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>756696</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7458623</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023, Norrbottens län</t>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113539124</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87325</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vaxspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius pinophilus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nietsavaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>756875</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7458472</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112022240</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nietsavaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>756850</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7458466</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112376645</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>väster om Nietsavaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>756749</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7458438</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111466721</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nietsavaara nordväst-E10, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>756550</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7458627</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111466702</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nietsavaara nordväst-E10, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>756584</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7458603</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113539137</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90699</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>245044</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallmusseron</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tricholoma roseoacerbum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>A.Riva</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nietsavaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>756729</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7458438</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111466752</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87189</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>249254</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mospindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius areni-silvae</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brandrud) Brandrud</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nietsavaara nordväst-E10, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>756582</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7458606</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 15155-2025 artfynd.xlsx
+++ b/artfynd/A 15155-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113539153</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112022147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112022148</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112376561</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112376510</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466666</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113539124</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112022240</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112376645</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466721</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1786,6 +1841,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466702</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113539137</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,8 +2053,28 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466752</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>